--- a/config/节点表头映射关系.xlsx
+++ b/config/节点表头映射关系.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>中文表头</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -454,11 +449,6 @@
           <t>编号</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>原数据保留</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -476,11 +466,6 @@
           <t>类型</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>根据节点相连道路映射后的道路等级进行判断，但先全部按“信号控制交叉口”输入</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -496,11 +481,6 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>geometry</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>excel中保留原数据，形成shp则需要利用geopandas替换该列数据为实际的矢量数据</t>
         </is>
       </c>
     </row>

--- a/config/节点表头映射关系.xlsx
+++ b/config/节点表头映射关系.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,15 +470,49 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>经度</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>x_coord</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>经度</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>纬度</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>y_coord</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>纬度</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>矢量数据</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>geometry</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>geometry</t>
         </is>
